--- a/Data/EXCEL/Transfer/salemon/202412/6404-salemon-202412.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202412/6404-salemon-202412.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\202412\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202412\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{34D1E171-A68D-43B5-967D-0B8422CDF519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{924AE507-173D-457D-968E-E9F1C8FAAF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{23196F01-E209-48EE-97B7-BF923E0A100F}"/>
+    <workbookView xWindow="2235" yWindow="1695" windowWidth="21600" windowHeight="13425" xr2:uid="{A95CB5F7-E47F-4084-B151-ED4E02CC6268}"/>
   </bookViews>
   <sheets>
     <sheet name="6404-salemon-202412" sheetId="2" r:id="rId1"/>
@@ -1258,24 +1258,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D12B68D-AD6D-4F77-B09A-A7F7B41862E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55483CD4-4DF4-4AFB-AEA8-88818B86F04E}">
   <dimension ref="A1:Q37"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.36328125" customWidth="1"/>
-    <col min="2" max="5" width="14.26953125" customWidth="1"/>
-    <col min="6" max="6" width="13.54296875" customWidth="1"/>
-    <col min="7" max="8" width="16.36328125" customWidth="1"/>
-    <col min="9" max="10" width="13.54296875" customWidth="1"/>
-    <col min="11" max="11" width="16.36328125" customWidth="1"/>
-    <col min="12" max="12" width="13.54296875" customWidth="1"/>
-    <col min="13" max="13" width="16.36328125" customWidth="1"/>
-    <col min="14" max="15" width="13.54296875" customWidth="1"/>
-    <col min="16" max="16" width="16.36328125" customWidth="1"/>
-    <col min="17" max="17" width="14.08984375" customWidth="1"/>
+    <col min="1" max="1" width="11.125" customWidth="1"/>
+    <col min="2" max="5" width="9.25" customWidth="1"/>
+    <col min="6" max="6" width="8.875" customWidth="1"/>
+    <col min="7" max="8" width="10.625" customWidth="1"/>
+    <col min="9" max="10" width="8.875" customWidth="1"/>
+    <col min="11" max="11" width="10.625" customWidth="1"/>
+    <col min="12" max="12" width="8.875" customWidth="1"/>
+    <col min="13" max="13" width="10.625" customWidth="1"/>
+    <col min="14" max="15" width="8.875" customWidth="1"/>
+    <col min="16" max="16" width="10.625" customWidth="1"/>
+    <col min="17" max="17" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1302,7 +1302,7 @@
       <c r="P1" s="20"/>
       <c r="Q1" s="21"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
       <c r="B2" s="16" t="s">
         <v>4</v>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="Q2" s="21"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -1384,7 +1384,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -1423,7 +1423,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>45413</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>-72.3</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>45383</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>-67.400000000000006</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>45352</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>-63.2</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>45323</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>-54.4</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>45292</v>
       </c>
@@ -1688,7 +1688,7 @@
         <v>-53.8</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>45261</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>45231</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>45200</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>34.200000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>45170</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>45139</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>45108</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>45078</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>45047</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>7.82</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>45017</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>44986</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>44958</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>6.04</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>44927</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>44896</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>-81.099999999999994</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>44866</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>-82.4</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>44835</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>-83.9</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>44805</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>-85.2</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>44774</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>-86.4</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>44743</v>
       </c>
@@ -2642,7 +2642,7 @@
         <v>-87.3</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>44713</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>-88.3</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>44682</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>-89.5</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>44652</v>
       </c>
@@ -2801,7 +2801,7 @@
         <v>-90.5</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>44621</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>-91.6</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>44593</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>-93.2</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>44562</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>-94.2</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <v>44531</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>-71.7</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>44501</v>
       </c>
@@ -3066,7 +3066,7 @@
         <v>-68.3</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <v>44470</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>-65</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>44440</v>
       </c>
